--- a/product_selector_out/STM32U535-545.xlsx
+++ b/product_selector_out/STM32U535-545.xlsx
@@ -7062,9 +7062,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -7389,9 +7389,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -7716,9 +7716,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -8043,9 +8043,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -8370,9 +8370,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -8697,9 +8697,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -9024,9 +9024,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -9351,9 +9351,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -9678,9 +9678,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -10005,9 +10005,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -10332,9 +10332,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -10659,9 +10659,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -10986,9 +10986,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -11313,9 +11313,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -11640,9 +11640,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -11967,9 +11967,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -12063,7 +12063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12156,19 +12156,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U535CE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12222,19 +12222,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U545VE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12244,19 +12244,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U545VE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12288,19 +12288,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12310,19 +12310,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12332,19 +12332,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12354,14 +12354,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -12376,14 +12376,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -12398,14 +12398,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -12420,19 +12420,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12442,19 +12442,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12464,19 +12464,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12486,19 +12486,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12508,19 +12508,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12530,19 +12530,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12552,19 +12552,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12574,19 +12574,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12596,19 +12596,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12618,14 +12618,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12647,7 +12647,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12669,7 +12669,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12684,19 +12684,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12706,19 +12706,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12728,19 +12728,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12750,19 +12750,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12772,19 +12772,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12794,19 +12794,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12816,19 +12816,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12845,12 +12845,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12860,19 +12860,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12882,14 +12882,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12926,14 +12926,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12948,19 +12948,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12970,19 +12970,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12999,12 +12999,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13014,19 +13014,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13036,19 +13036,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13058,19 +13058,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13080,19 +13080,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U535NC</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13109,12 +13109,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U535NC</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13124,29 +13124,381 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>STM32U535JE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>STM32U535NC</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32U535NC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32U535NC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32U535NC</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32U535-545.xlsx
+++ b/product_selector_out/STM32U535-545.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM27"/>
+  <dimension ref="A1:BN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.73828125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -6219,12 +6301,17 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6245,16 +6332,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6267,6 +6352,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6286,7 +6372,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6319,7 +6407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM27"/>
+  <dimension ref="A1:BN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6387,6 +6475,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6720,6 +6809,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6815,6 +6909,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7137,7 +7232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7464,7 +7564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7791,7 +7896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8118,7 +8228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8445,7 +8560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8772,7 +8892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9099,7 +9224,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9426,7 +9556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9753,7 +9888,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10080,7 +10220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10407,7 +10552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10734,7 +10884,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11061,7 +11216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11388,7 +11548,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11715,7 +11880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12042,7 +12212,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12050,8 +12225,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
